--- a/conditions/introduction.xlsx
+++ b/conditions/introduction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pahr0811/Documents/PhD/Year_1/Study_1/PsychoPy_experiment/creaky_experiment/conditions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48531A1E-C6B2-EA41-93CB-BC04F8E74D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CF43E2-CD24-204B-B5BC-0E07AB7C637B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="29040" windowHeight="17640" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>introductory_stimuli/creak_m_3.wav</t>
   </si>
   <si>
-    <t>This is another example of vocal fry.  (2 of 6)</t>
-  </si>
-  <si>
     <t>This is another example of vocal fry. (3 of 6)</t>
   </si>
   <si>
@@ -75,6 +72,9 @@
   </si>
   <si>
     <t>This is an example of vocal fry. (1 of 6)</t>
+  </si>
+  <si>
+    <t>This is another example of vocal fry. (2 of 6)</t>
   </si>
 </sst>
 </file>
@@ -734,7 +734,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -742,7 +742,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -750,7 +750,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -758,7 +758,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -766,7 +766,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -774,7 +774,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -784,15 +784,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="805e3853-2971-4830-a200-7929f1998a0d">
@@ -801,6 +792,15 @@
     <TaxCatchAll xmlns="1abb6105-976e-4641-94d5-932be0f0089d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -993,14 +993,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8FE25B-F2A6-404B-BFAA-4FDF41C79620}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1009,6 +1001,14 @@
     <ds:schemaRef ds:uri="d7532cd0-e888-47d6-8f58-db0210f25002"/>
     <ds:schemaRef ds:uri="805e3853-2971-4830-a200-7929f1998a0d"/>
     <ds:schemaRef ds:uri="1abb6105-976e-4641-94d5-932be0f0089d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
